--- a/tests/Browser/Excel/GiamSat.xlsx
+++ b/tests/Browser/Excel/GiamSat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TuDongLamViec\tests\Browser\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EE1337-5D41-4541-9881-1DBC4317F6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C93155-BD90-40A0-877E-F1CF0FE09144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
+    <workbookView xWindow="3980" yWindow="2830" windowWidth="19200" windowHeight="10060" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>loai_tt</t>
   </si>
@@ -57,12 +57,6 @@
     <t>Khảo sát</t>
   </si>
   <si>
-    <t>41|42|43|44</t>
-  </si>
-  <si>
-    <t>41|42|43|44|45</t>
-  </si>
-  <si>
     <t>quyet_dinh_ten</t>
   </si>
   <si>
@@ -93,22 +87,28 @@
     <t>tailieu1.pdf|tailieu2.pdf|tailieu3.pdf</t>
   </si>
   <si>
-    <t>6|7|8|9|10</t>
-  </si>
-  <si>
-    <t>6|7|8|9|10|11</t>
-  </si>
-  <si>
-    <t>6|7|8|9|10|11|12</t>
-  </si>
-  <si>
-    <t>6|7|8</t>
-  </si>
-  <si>
-    <t>Giám sát vấn đề 10/9/2026</t>
-  </si>
-  <si>
-    <t>Khảo sát vấn đề 10/9/2026</t>
+    <t>HĐND tỉnh</t>
+  </si>
+  <si>
+    <t>Trực tiếp</t>
+  </si>
+  <si>
+    <t>Gián tiếp</t>
+  </si>
+  <si>
+    <t>Giám sát vấn đề 16/9/2026</t>
+  </si>
+  <si>
+    <t>Khảo sát vấn đề 16/9/2026</t>
+  </si>
+  <si>
+    <t>Xã Bình Yên|Xã Trung Hội</t>
+  </si>
+  <si>
+    <t>Xã An Khánh|Phường Đức Xuân</t>
+  </si>
+  <si>
+    <t>Tài liệu của UBND Tỉnh|Tài liệu của TT HĐND Tỉnh|Tài liệu của TT HĐND Tỉnh</t>
   </si>
 </sst>
 </file>
@@ -499,7 +499,7 @@
     <col min="8" max="8" width="18.36328125" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="24.1796875" customWidth="1"/>
-    <col min="11" max="11" width="23.54296875" customWidth="1"/>
+    <col min="11" max="11" width="41.54296875" customWidth="1"/>
     <col min="12" max="12" width="27.08984375" customWidth="1"/>
     <col min="13" max="13" width="15.81640625" customWidth="1"/>
   </cols>
@@ -512,10 +512,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -536,10 +536,10 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -548,20 +548,20 @@
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
-        <v>7</v>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3">
         <v>46268</v>
@@ -570,16 +570,16 @@
         <v>46295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -588,20 +588,20 @@
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2">
-        <v>5</v>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3">
         <v>46268</v>
@@ -610,16 +610,16 @@
         <v>46325</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
